--- a/astro-site/public/dl/kit-inventario/05-control-mermas.xlsx
+++ b/astro-site/public/dl/kit-inventario/05-control-mermas.xlsx
@@ -1,19 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Registro Diario Mermas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Análisis por Categoría" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Dashboard Mermas" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Plan de Acción" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registro Diario Mermas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Análisis por Categoría" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard Mermas" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan de Acción" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Registro Diario Mermas'!$3:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Análisis por Categoría'!$3:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Dashboard Mermas'!$3:$3</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -116,44 +120,44 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="16">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="3" numFmtId="4" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="3" numFmtId="4" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -513,12 +517,12 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="80"/>
+    <col width="80" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -593,8 +597,25 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-inventario · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -603,21 +624,21 @@
   <sheetPr>
     <tabColor rgb="00FF4444"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="12"/>
-    <col customWidth="1" max="2" min="2" width="22"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="10"/>
-    <col customWidth="1" max="5" min="5" width="8"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
-    <col customWidth="1" max="8" min="8" width="18"/>
-    <col customWidth="1" max="9" min="9" width="14"/>
-    <col customWidth="1" max="10" min="10" width="25"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -627,6 +648,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -1429,6 +1451,7 @@
       <c r="I53" s="9" t="n"/>
       <c r="J53" s="9" t="n"/>
     </row>
+    <row r="54"/>
     <row r="55">
       <c r="F55" s="11" t="inlineStr">
         <is>
@@ -1437,7 +1460,7 @@
       </c>
       <c r="G55" s="12">
         <f>SUM(G4:G53)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
   </sheetData>
@@ -1445,11 +1468,20 @@
     <mergeCell ref="A1:J1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="0" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="H4 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51 H52 H53" type="list">
+    <dataValidation sqref="H4 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51 H52 H53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Caducidad,Preparación,Devolución,Accidente,Sobreproducción,Deterioro,Otro"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1458,16 +1490,16 @@
   <sheetPr>
     <tabColor rgb="00FFB800"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="18"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="22"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1477,6 +1509,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -1585,7 +1618,16 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1594,15 +1636,15 @@
   <sheetPr>
     <tabColor rgb="0000C853"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="22"/>
-    <col customWidth="1" max="2" min="2" width="22"/>
-    <col customWidth="1" max="3" min="3" width="22"/>
-    <col customWidth="1" max="4" min="4" width="22"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1612,6 +1654,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
         <is>
@@ -1640,13 +1683,11 @@
           <t>Coste total mermas (€)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>&lt; 500 €</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1654,13 +1695,11 @@
           <t>% mermas / compras</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>&lt; 3%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1668,13 +1707,11 @@
           <t>Nº incidencias</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>&lt; 20</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1682,13 +1719,11 @@
           <t>Categoría con más merma</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1696,16 +1731,23 @@
           <t>Motivo más frecuente</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1714,18 +1756,18 @@
   <sheetPr>
     <tabColor rgb="0043A047"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="10"/>
-    <col customWidth="1" max="2" min="2" width="14"/>
-    <col customWidth="1" max="3" min="3" width="25"/>
-    <col customWidth="1" max="4" min="4" width="30"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
-    <col customWidth="1" max="7" min="7" width="12"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1735,6 +1777,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -1772,10 +1815,20 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>